--- a/report/test_results_search.xlsx
+++ b/report/test_results_search.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,7 +537,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -618,7 +616,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -656,7 +653,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -669,8 +665,6 @@
           <t>test_search_6</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Please fill out this field.</t>
@@ -686,7 +680,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -724,7 +717,44 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-08 21:46:27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test_search_1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sách</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sách</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Có 10 kết quả tìm kiếm phù hợp</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CÓ 10 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/report/test_results_search.xlsx
+++ b/report/test_results_search.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,298 +463,6 @@
           <t>Screenshot</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:15:14</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>test_search_1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>sách</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sách</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Có 10 kết quả tìm kiếm phù hợp</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CÓ 10 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:15:33</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>test_search_2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Có 6 kết quả tìm kiếm phù hợp</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CÓ 6 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:15:46</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>test_search_3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>trắng</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>trắng</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Có 116 kết quả tìm kiếm phù hợp</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CÓ 123 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>report/screenshots\test_search_3.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:15:57</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>test_search_4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Có 14 kết quả tìm kiếm phù hợp</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CÓ 14 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:16:09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>test_search_5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>agh1234</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>agh1234</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN. | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:16:19</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>test_search_6</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:16:34</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>test_search_7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>!@#$%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>!@#$%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN. | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-05-08 21:46:27</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>test_search_1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>sách</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>sách</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Có 10 kết quả tìm kiếm phù hợp</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CÓ 10 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/report/test_results_search.xlsx
+++ b/report/test_results_search.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,936 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:24:22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>test_search_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sách</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sách</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Có 10 kết quả tìm kiếm phù hợp</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CÓ 10 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:24:31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test_search_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Có 6 kết quả tìm kiếm phù hợp</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CÓ 6 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:24:42</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test_search_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>trắng</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>trắng</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Có 131 kết quả tìm kiếm phù hợp</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CÓ 131 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:24:52</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_search_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Có 14 kết quả tìm kiếm phù hợp</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CÓ 14 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:25:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_search_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>agh1234</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>agh1234</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:25:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test_search_6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:25:19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test_search_7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>!@#$%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>!@#$%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:25:36</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test_search_8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>thước</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>thước</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ TÌM KIẾM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CÓ 31 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:25:49</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>test_search_9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:26:04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>test_search_10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>vở</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>vở</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ TÌM KIẾM</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CÓ 30 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:26:18</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>test_search_11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gôm</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>gôm</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ TÌM KIẾM</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CÓ 26 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:26:31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>test_search_12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:26:42</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>test_search_13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>gôm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>gôm</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ TÌM KIẾM</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CÓ 26 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:26:50</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>test_search_14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:26:58</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>test_search_15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:27:06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>test_search_16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:27:14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>test_search_17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:27:23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>test_search_18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>vở</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>vở</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ TÌM KIẾM</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CÓ 30 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:27:31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>test_search_19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:27:41</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>test_search_20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:27:51</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>test_search_21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>vở</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>vở</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ TÌM KIẾM</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CÓ 30 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:27:58</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>test_search_22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:28:08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>test_search_23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:28:26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>test_search_24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>vở</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>vở</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ TÌM KIẾM</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CÓ 30 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:28:35</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>test_search_25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:28:45</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>test_search_26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>bút</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>bút</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ TÌM KIẾM</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CÓ 759 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:28:57</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>test_search_27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>thước</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>thước</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ TÌM KIẾM</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CÓ 31 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/test_results_search.xlsx
+++ b/report/test_results_search.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,264 +463,6 @@
           <t>Screenshot</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-14 23:11:29</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>test_search_1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>sách</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sách</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Có 10 kết quả tìm kiếm phù hợp</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CÓ 10 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-14 23:11:43</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>test_search_2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Có 6 kết quả tìm kiếm phù hợp</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CÓ 6 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-14 23:11:52</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>test_search_3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>trắng</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>trắng</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CÓ 130 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CÓ 130 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-14 23:12:04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>test_search_4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Có 14 kết quả tìm kiếm phù hợp</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CÓ 14 KẾT QUẢ TÌM KIẾM PHÙ HỢP | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-14 23:12:13</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>test_search_5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>agh1234</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>agh1234</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN. | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-14 23:12:21</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>test_search_6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-14 23:12:32</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>test_search_7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>!@#$%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>!@#$%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN. | Please fill out this field.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/report/test_results_search.xlsx
+++ b/report/test_results_search.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,6 +463,264 @@
           <t>Screenshot</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:31:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>test_search_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>áo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>áo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Có 224 kết quả tìm kiếm phù hợp</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CÓ 224 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:31:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test_search_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>q</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:31:50</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test_search_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>đen</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CÓ 201 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CÓ 201 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:31:58</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_search_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:32:07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_search_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>agh1234</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>agh1234</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:32:14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test_search_6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:32:22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test_search_7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>!@#$%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>!@#$%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Không tìm thấy bất kỳ kết quả nào với từ khóa trên.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KHÔNG TÌM THẤY BẤT KỲ KẾT QUẢ NÀO VỚI TỪ KHÓA TRÊN.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
